--- a/examples/05-rich-text.xlsx
+++ b/examples/05-rich-text.xlsx
@@ -46,8 +46,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,10 +419,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,7 +489,178 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <r>
+            <t>H</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>2</t>
+          </r>
+          <r>
+            <t>O and CO</t>
+          </r>
+          <r>
+            <rPr>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>2</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <strike val="1"/>
+              <color rgb="FF7F7F7F"/>
+            </rPr>
+            <t>old price 120</t>
+          </r>
+          <r>
+            <t> </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="FFC00000"/>
+              <sz val="14"/>
+            </rPr>
+            <t>99</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> UAH</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>Line one</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <i val="1"/>
+              <color rgb="FF2F5597"/>
+            </rPr>
+            <t>line two</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <u val="double"/>
+            </rPr>
+            <t>line three</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Georgia"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">Georgia </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Verdana"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Verdana </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <i val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Times</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">日本語 </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+            </rPr>
+            <t>太字</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> · Ελληνικά </t>
+          </r>
+          <r>
+            <rPr>
+              <i val="1"/>
+            </rPr>
+            <t>πλάγια</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> · ✅</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="FF1F4E79"/>
+              <sz val="13"/>
+            </rPr>
+            <t xml:space="preserve">Merged: </t>
+          </r>
+          <r>
+            <t>rich text spanning three columns and two rows</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Plain text next to a formula</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>LEN(A13)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A10:C11"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>